--- a/estimates/output/jhr_se16/jhr_se16_estimates.xlsx
+++ b/estimates/output/jhr_se16/jhr_se16_estimates.xlsx
@@ -583,13 +583,13 @@
         <v>1461042</v>
       </c>
       <c r="E4" t="n">
-        <v>75.13</v>
+        <v>75.44</v>
       </c>
       <c r="F4" t="n">
-        <v>74.06999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="G4" t="n">
-        <v>76.16</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>52.73</v>
@@ -641,13 +641,13 @@
         <v>1461042</v>
       </c>
       <c r="E5" t="n">
-        <v>63.71</v>
+        <v>63.73</v>
       </c>
       <c r="F5" t="n">
-        <v>61.72</v>
+        <v>61.91</v>
       </c>
       <c r="G5" t="n">
-        <v>65.43000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>34.28</v>
@@ -699,13 +699,13 @@
         <v>1461042</v>
       </c>
       <c r="E6" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="H6" t="n">
         <v>0.53</v>
@@ -757,13 +757,13 @@
         <v>1461042</v>
       </c>
       <c r="E7" t="n">
-        <v>6.8</v>
+        <v>6.39</v>
       </c>
       <c r="F7" t="n">
-        <v>5.36</v>
+        <v>4.94</v>
       </c>
       <c r="G7" t="n">
-        <v>8.619999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="H7" t="n">
         <v>2.17</v>
@@ -815,13 +815,13 @@
         <v>981403</v>
       </c>
       <c r="E8" t="n">
-        <v>62.29</v>
+        <v>62.4</v>
       </c>
       <c r="F8" t="n">
-        <v>60.89</v>
+        <v>61.05</v>
       </c>
       <c r="G8" t="n">
-        <v>63.77</v>
+        <v>63.97</v>
       </c>
       <c r="H8" t="n">
         <v>36.56</v>
@@ -873,13 +873,13 @@
         <v>981403</v>
       </c>
       <c r="E9" t="n">
-        <v>7.73</v>
+        <v>7.42</v>
       </c>
       <c r="F9" t="n">
-        <v>6.28</v>
+        <v>6.22</v>
       </c>
       <c r="G9" t="n">
-        <v>9.84</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>1.03</v>
@@ -931,13 +931,13 @@
         <v>981403</v>
       </c>
       <c r="E10" t="n">
-        <v>52.53</v>
+        <v>52.39</v>
       </c>
       <c r="F10" t="n">
-        <v>51.33</v>
+        <v>51.03</v>
       </c>
       <c r="G10" t="n">
-        <v>53.73</v>
+        <v>53.56</v>
       </c>
       <c r="H10" t="n">
         <v>12.64</v>
@@ -989,13 +989,13 @@
         <v>981403</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03</v>
+        <v>0.44</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1047,13 +1047,13 @@
         <v>193096</v>
       </c>
       <c r="E12" t="n">
-        <v>53.85</v>
+        <v>51.88</v>
       </c>
       <c r="F12" t="n">
-        <v>48.47</v>
+        <v>44.98</v>
       </c>
       <c r="G12" t="n">
-        <v>59.05</v>
+        <v>58.3</v>
       </c>
       <c r="H12" t="n">
         <v>1.66</v>
@@ -1105,13 +1105,13 @@
         <v>193096</v>
       </c>
       <c r="E13" t="n">
-        <v>26.14</v>
+        <v>26.92</v>
       </c>
       <c r="F13" t="n">
-        <v>19.4</v>
+        <v>20.85</v>
       </c>
       <c r="G13" t="n">
-        <v>32.41</v>
+        <v>32.28</v>
       </c>
       <c r="H13" t="n">
         <v>0.26</v>
@@ -1163,13 +1163,13 @@
         <v>193096</v>
       </c>
       <c r="E14" t="n">
-        <v>17.13</v>
+        <v>18.03</v>
       </c>
       <c r="F14" t="n">
-        <v>13.05</v>
+        <v>13.69</v>
       </c>
       <c r="G14" t="n">
-        <v>20.77</v>
+        <v>22.4</v>
       </c>
       <c r="H14" t="n">
         <v>0.02</v>
@@ -1221,13 +1221,13 @@
         <v>193096</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01</v>
+        <v>3.38</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         <v>67634</v>
       </c>
       <c r="E16" t="n">
-        <v>60.02</v>
+        <v>57.29</v>
       </c>
       <c r="F16" t="n">
-        <v>50.11</v>
+        <v>46.77</v>
       </c>
       <c r="G16" t="n">
-        <v>64.81999999999999</v>
+        <v>63.02</v>
       </c>
       <c r="H16" t="n">
         <v>2.5</v>
@@ -1337,13 +1337,13 @@
         <v>67634</v>
       </c>
       <c r="E17" t="n">
-        <v>46.51</v>
+        <v>48.31</v>
       </c>
       <c r="F17" t="n">
-        <v>36.69</v>
+        <v>37.48</v>
       </c>
       <c r="G17" t="n">
-        <v>53.66</v>
+        <v>54.99</v>
       </c>
       <c r="H17" t="n">
         <v>1.24</v>
@@ -1395,13 +1395,13 @@
         <v>67634</v>
       </c>
       <c r="E18" t="n">
-        <v>5.75</v>
+        <v>5.43</v>
       </c>
       <c r="F18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="G18" t="n">
-        <v>8.619999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="H18" t="n">
         <v>0.13</v>
@@ -1453,13 +1453,13 @@
         <v>67634</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>663898</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="F20" t="n">
         <v>64.42</v>
       </c>
       <c r="G20" t="n">
-        <v>67.63</v>
+        <v>67.59</v>
       </c>
       <c r="H20" t="n">
         <v>54.42</v>
@@ -1569,13 +1569,13 @@
         <v>663898</v>
       </c>
       <c r="E21" t="n">
-        <v>42.79</v>
+        <v>42.78</v>
       </c>
       <c r="F21" t="n">
-        <v>39.78</v>
+        <v>39.8</v>
       </c>
       <c r="G21" t="n">
-        <v>45.84</v>
+        <v>45.85</v>
       </c>
       <c r="H21" t="n">
         <v>31.48</v>
@@ -1627,13 +1627,13 @@
         <v>663898</v>
       </c>
       <c r="E22" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="F22" t="n">
-        <v>15.54</v>
+        <v>15.52</v>
       </c>
       <c r="G22" t="n">
-        <v>19.72</v>
+        <v>19.73</v>
       </c>
       <c r="H22" t="n">
         <v>11.8</v>
@@ -1685,13 +1685,13 @@
         <v>663898</v>
       </c>
       <c r="E23" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="F23" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="G23" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
       <c r="H23" t="n">
         <v>1.61</v>
@@ -1743,13 +1743,13 @@
         <v>582037</v>
       </c>
       <c r="E24" t="n">
-        <v>65.61</v>
+        <v>65.62</v>
       </c>
       <c r="F24" t="n">
-        <v>64.31999999999999</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>66.78</v>
+        <v>66.8</v>
       </c>
       <c r="H24" t="n">
         <v>42.88</v>
@@ -1801,13 +1801,13 @@
         <v>582037</v>
       </c>
       <c r="E25" t="n">
-        <v>41.94</v>
+        <v>41.93</v>
       </c>
       <c r="F25" t="n">
-        <v>39.58</v>
+        <v>39.57</v>
       </c>
       <c r="G25" t="n">
-        <v>44.46</v>
+        <v>44.44</v>
       </c>
       <c r="H25" t="n">
         <v>20.88</v>
@@ -1859,13 +1859,13 @@
         <v>582037</v>
       </c>
       <c r="E26" t="n">
-        <v>18.2</v>
+        <v>18.19</v>
       </c>
       <c r="F26" t="n">
-        <v>16.12</v>
+        <v>16.14</v>
       </c>
       <c r="G26" t="n">
-        <v>20.12</v>
+        <v>20.1</v>
       </c>
       <c r="H26" t="n">
         <v>7.24</v>
@@ -1917,13 +1917,13 @@
         <v>582037</v>
       </c>
       <c r="E27" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="F27" t="n">
         <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
         <v>0.75</v>
@@ -1975,13 +1975,13 @@
         <v>494571</v>
       </c>
       <c r="E28" t="n">
-        <v>68.34</v>
+        <v>68.33</v>
       </c>
       <c r="F28" t="n">
-        <v>67.17</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>69.5</v>
+        <v>69.47</v>
       </c>
       <c r="H28" t="n">
         <v>44.54</v>
@@ -2033,13 +2033,13 @@
         <v>494571</v>
       </c>
       <c r="E29" t="n">
-        <v>40.84</v>
+        <v>40.8</v>
       </c>
       <c r="F29" t="n">
-        <v>38.09</v>
+        <v>38.03</v>
       </c>
       <c r="G29" t="n">
-        <v>43.72</v>
+        <v>43.66</v>
       </c>
       <c r="H29" t="n">
         <v>17.7</v>
@@ -2091,13 +2091,13 @@
         <v>494571</v>
       </c>
       <c r="E30" t="n">
-        <v>20.7</v>
+        <v>20.77</v>
       </c>
       <c r="F30" t="n">
-        <v>18.43</v>
+        <v>18.49</v>
       </c>
       <c r="G30" t="n">
-        <v>22.83</v>
+        <v>22.98</v>
       </c>
       <c r="H30" t="n">
         <v>7.19</v>
@@ -2149,13 +2149,13 @@
         <v>494571</v>
       </c>
       <c r="E31" t="n">
-        <v>4.63</v>
+        <v>4.54</v>
       </c>
       <c r="F31" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="G31" t="n">
-        <v>6.04</v>
+        <v>6.03</v>
       </c>
       <c r="H31" t="n">
         <v>0.73</v>
@@ -2207,13 +2207,13 @@
         <v>398733</v>
       </c>
       <c r="E32" t="n">
-        <v>74.56999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>73.41</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>75.77</v>
+        <v>75.81</v>
       </c>
       <c r="H32" t="n">
         <v>48.05</v>
@@ -2268,10 +2268,10 @@
         <v>38.55</v>
       </c>
       <c r="F33" t="n">
-        <v>35.88</v>
+        <v>35.87</v>
       </c>
       <c r="G33" t="n">
-        <v>41.67</v>
+        <v>41.68</v>
       </c>
       <c r="H33" t="n">
         <v>14.35</v>
@@ -2323,13 +2323,13 @@
         <v>398733</v>
       </c>
       <c r="E34" t="n">
-        <v>28.96</v>
+        <v>28.93</v>
       </c>
       <c r="F34" t="n">
-        <v>26.3</v>
+        <v>26.25</v>
       </c>
       <c r="G34" t="n">
-        <v>31.54</v>
+        <v>31.51</v>
       </c>
       <c r="H34" t="n">
         <v>10.31</v>
@@ -2381,13 +2381,13 @@
         <v>398733</v>
       </c>
       <c r="E35" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="F35" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="G35" t="n">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="H35" t="n">
         <v>0.43</v>
@@ -2439,13 +2439,13 @@
         <v>313976</v>
       </c>
       <c r="E36" t="n">
-        <v>79.26000000000001</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>78.42</v>
+        <v>78.39</v>
       </c>
       <c r="G36" t="n">
-        <v>80.3</v>
+        <v>80.34</v>
       </c>
       <c r="H36" t="n">
         <v>46.57</v>
@@ -2497,13 +2497,13 @@
         <v>313976</v>
       </c>
       <c r="E37" t="n">
-        <v>41.02</v>
+        <v>41</v>
       </c>
       <c r="F37" t="n">
-        <v>38.22</v>
+        <v>38.1</v>
       </c>
       <c r="G37" t="n">
-        <v>44.11</v>
+        <v>44.09</v>
       </c>
       <c r="H37" t="n">
         <v>11.63</v>
@@ -2555,13 +2555,13 @@
         <v>313976</v>
       </c>
       <c r="E38" t="n">
-        <v>32.04</v>
+        <v>32.03</v>
       </c>
       <c r="F38" t="n">
-        <v>28.93</v>
+        <v>29.03</v>
       </c>
       <c r="G38" t="n">
-        <v>34.89</v>
+        <v>34.77</v>
       </c>
       <c r="H38" t="n">
         <v>11.02</v>
@@ -2613,13 +2613,13 @@
         <v>313976</v>
       </c>
       <c r="E39" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="F39" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="H39" t="n">
         <v>0.17</v>
@@ -2671,13 +2671,13 @@
         <v>249960</v>
       </c>
       <c r="E40" t="n">
-        <v>59.71</v>
+        <v>59.75</v>
       </c>
       <c r="F40" t="n">
-        <v>57.67</v>
+        <v>57.77</v>
       </c>
       <c r="G40" t="n">
-        <v>61.68</v>
+        <v>61.58</v>
       </c>
       <c r="H40" t="n">
         <v>40.37</v>
@@ -2729,13 +2729,13 @@
         <v>249960</v>
       </c>
       <c r="E41" t="n">
-        <v>30.38</v>
+        <v>30.53</v>
       </c>
       <c r="F41" t="n">
-        <v>27.05</v>
+        <v>27.14</v>
       </c>
       <c r="G41" t="n">
-        <v>33.81</v>
+        <v>33.75</v>
       </c>
       <c r="H41" t="n">
         <v>9.369999999999999</v>
@@ -2787,13 +2787,13 @@
         <v>249960</v>
       </c>
       <c r="E42" t="n">
-        <v>24.82</v>
+        <v>24.71</v>
       </c>
       <c r="F42" t="n">
-        <v>22.14</v>
+        <v>21.94</v>
       </c>
       <c r="G42" t="n">
-        <v>27.72</v>
+        <v>27.48</v>
       </c>
       <c r="H42" t="n">
         <v>9.1</v>
@@ -2845,13 +2845,13 @@
         <v>249960</v>
       </c>
       <c r="E43" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="F43" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G43" t="n">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="H43" t="n">
         <v>0.01</v>
@@ -12477,7 +12477,7 @@
         <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -12500,10 +12500,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -12526,7 +12526,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0.05</v>
@@ -12555,7 +12555,7 @@
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -12581,7 +12581,7 @@
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -12607,7 +12607,7 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -12633,7 +12633,7 @@
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -12659,7 +12659,7 @@
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -12708,10 +12708,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.04</v>
+        <v>-0.43</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -12786,7 +12786,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03</v>
+        <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.27</v>
+        <v>-0.58</v>
       </c>
       <c r="E20" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -12916,10 +12916,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -12942,10 +12942,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.05</v>
+        <v>-0.88</v>
       </c>
       <c r="E24" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -12994,10 +12994,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="E25" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -13020,10 +13020,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.36</v>
+        <v>1.11</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -13046,10 +13046,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="E27" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
